--- a/docs/downloads/04/tbl_other_educ_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_sex_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,10 +398,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E2">
-        <v>36.3</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="3">
@@ -463,14 +463,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6">
@@ -481,19 +481,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="E6">
-        <v>0.6</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="7">
@@ -509,14 +509,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D7">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="E7">
-        <v>38.5</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="8">
@@ -532,14 +532,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D8">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="E8">
-        <v>45.7</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="9">
@@ -555,60 +555,60 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E9">
-        <v>14.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="E10">
-        <v>1.3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="E11">
-        <v>0.4</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="12">
@@ -624,14 +624,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D12">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +647,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D13">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="E13">
-        <v>46.7</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="14">
@@ -665,19 +665,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D14">
         <v>51</v>
       </c>
       <c r="E14">
-        <v>19.8</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="15">
@@ -688,19 +688,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="E15">
-        <v>5.1</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="16">
@@ -711,19 +711,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E16">
-        <v>0.4</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -739,14 +739,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D17">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="E17">
-        <v>37</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="18">
@@ -755,108 +755,102 @@
           <t>Marovoay - Bepako</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>70</v>
-      </c>
-      <c r="E18">
-        <v>45.5</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="E19">
-        <v>9.699999999999999</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>121</v>
       </c>
       <c r="E20">
-        <v>5.8</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E21">
-        <v>1.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="23">
@@ -867,7 +861,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -876,10 +870,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E23">
-        <v>31</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="24">
@@ -890,7 +884,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -899,10 +893,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="E24">
-        <v>52.2</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="25">
@@ -913,7 +907,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -922,10 +916,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E25">
-        <v>15.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="26">
@@ -936,19 +930,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="27">
@@ -957,108 +951,102 @@
           <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>80</v>
-      </c>
-      <c r="E27">
-        <v>50.3</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D28">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E28">
-        <v>41.5</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D29">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="E29">
-        <v>6.9</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="E30">
-        <v>1.3</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>100</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="32">
@@ -1069,7 +1057,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1078,10 +1066,10 @@
         </is>
       </c>
       <c r="D32">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E32">
-        <v>21.5</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="33">
@@ -1092,7 +1080,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1101,10 +1089,10 @@
         </is>
       </c>
       <c r="D33">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="E33">
-        <v>54.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="34">
@@ -1115,7 +1103,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1124,10 +1112,10 @@
         </is>
       </c>
       <c r="D34">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="E34">
-        <v>21.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1138,25 +1126,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1166,89 +1154,89 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>282</v>
       </c>
       <c r="E36">
-        <v>0.8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D37">
-        <v>70</v>
+        <v>521</v>
       </c>
       <c r="E37">
-        <v>38.3</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D38">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="E38">
-        <v>49.2</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D39">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E39">
-        <v>9.300000000000001</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1258,20 +1246,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>272</v>
       </c>
       <c r="E40">
-        <v>2.7</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1281,14 +1269,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>333</v>
       </c>
       <c r="E41">
-        <v>0.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="42">
@@ -1299,19 +1287,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D42">
-        <v>310</v>
+        <v>76</v>
       </c>
       <c r="E42">
-        <v>29.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="43">
@@ -1322,19 +1310,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D43">
-        <v>521</v>
+        <v>49</v>
       </c>
       <c r="E43">
-        <v>49.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="44">
@@ -1343,21 +1331,10 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
       <c r="C44" t="inlineStr">
         <is>
           <t>Secondaire 1er cycle</t>
         </is>
-      </c>
-      <c r="D44">
-        <v>179</v>
-      </c>
-      <c r="E44">
-        <v>17.1</v>
       </c>
     </row>
     <row r="45">
@@ -1366,195 +1343,10 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>31</v>
-      </c>
-      <c r="E45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>5</v>
-      </c>
-      <c r="E46">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>297</v>
-      </c>
-      <c r="E47">
-        <v>40.7</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>333</v>
-      </c>
-      <c r="E48">
-        <v>45.6</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>76</v>
-      </c>
-      <c r="E49">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>19</v>
-      </c>
-      <c r="E50">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>5</v>
-      </c>
-      <c r="E51">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53">
-        <v>50</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_other_educ_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_sex_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,10 +398,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>34.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -417,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D3">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="E3">
-        <v>47.3</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +440,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="E4">
-        <v>12.9</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="5">
@@ -463,14 +463,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>5.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="6">
@@ -481,19 +481,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D6">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>35.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="7">
@@ -509,14 +509,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D7">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>45.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -532,14 +532,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="E8">
-        <v>14.1</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="9">
@@ -555,60 +555,60 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="E9">
-        <v>4.7</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D10">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Ampijoroa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D11">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="E11">
-        <v>46.7</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="12">
@@ -624,14 +624,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D12">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>19.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +647,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D13">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E13">
-        <v>10.5</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="14">
@@ -665,19 +665,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D14">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="E14">
-        <v>33.1</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="15">
@@ -688,19 +688,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D15">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E15">
-        <v>45.5</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="16">
@@ -711,19 +711,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E16">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="17">
@@ -739,14 +739,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D17">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>11.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="18">
@@ -755,102 +755,102 @@
           <t>Marovoay - Bepako</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>46</v>
+      </c>
+      <c r="E18">
+        <v>29.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D19">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E19">
-        <v>28.9</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D20">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="E20">
-        <v>52.2</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D21">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E21">
-        <v>15.1</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Femme</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>9</v>
-      </c>
-      <c r="E22">
-        <v>3.9</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -861,7 +861,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E23">
-        <v>47.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="24">
@@ -884,19 +884,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D24">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E24">
-        <v>41.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -907,19 +907,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="E25">
-        <v>6.9</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="26">
@@ -930,19 +930,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E26">
-        <v>3.8</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="27">
@@ -951,21 +951,32 @@
           <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
+      </c>
+      <c r="D27">
+        <v>9</v>
+      </c>
+      <c r="E27">
+        <v>3.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -974,85 +985,85 @@
         </is>
       </c>
       <c r="D28">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E28">
-        <v>20.3</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D29">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="E29">
-        <v>54.1</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D30">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E30">
-        <v>21.5</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E31">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1062,37 +1073,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D32">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>33.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Homme</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>90</v>
-      </c>
-      <c r="E33">
-        <v>49.2</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1103,19 +1103,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>17</v>
-      </c>
-      <c r="E34">
-        <v>9.300000000000001</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1126,25 +1120,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D35">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E35">
-        <v>7.7</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1154,20 +1148,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D36">
-        <v>282</v>
+        <v>133</v>
       </c>
       <c r="E36">
-        <v>27</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1177,20 +1171,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D37">
-        <v>521</v>
+        <v>53</v>
       </c>
       <c r="E37">
-        <v>49.8</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1200,43 +1194,43 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D38">
-        <v>179</v>
+        <v>10</v>
       </c>
       <c r="E38">
-        <v>17.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D39">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="E39">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1246,20 +1240,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D40">
-        <v>272</v>
+        <v>48</v>
       </c>
       <c r="E40">
-        <v>37.3</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1273,16 +1267,16 @@
         </is>
       </c>
       <c r="D41">
-        <v>333</v>
+        <v>90</v>
       </c>
       <c r="E41">
-        <v>45.6</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1296,16 +1290,16 @@
         </is>
       </c>
       <c r="D42">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="E42">
-        <v>10.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1319,10 +1313,10 @@
         </is>
       </c>
       <c r="D43">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="E43">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="44">
@@ -1331,10 +1325,21 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>27</v>
+      </c>
+      <c r="E44">
+        <v>2.6</v>
       </c>
     </row>
     <row r="45">
@@ -1343,7 +1348,226 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>255</v>
+      </c>
+      <c r="E45">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>521</v>
+      </c>
+      <c r="E46">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>179</v>
+      </c>
+      <c r="E47">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>64</v>
+      </c>
+      <c r="E48">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>40</v>
+      </c>
+      <c r="E49">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>232</v>
+      </c>
+      <c r="E50">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>333</v>
+      </c>
+      <c r="E51">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>76</v>
+      </c>
+      <c r="E52">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>49</v>
+      </c>
+      <c r="E53">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>

--- a/docs/downloads/04/tbl_other_educ_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_sex_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -476,7 +476,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -568,7 +568,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -706,7 +706,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -902,7 +902,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -948,7 +948,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1017,7 +1017,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1040,7 +1040,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1086,7 +1086,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1138,7 +1138,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1230,7 +1230,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1253,7 +1253,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1276,7 +1276,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1322,7 +1322,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1414,7 +1414,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1437,7 +1437,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1460,7 +1460,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1529,7 +1529,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1552,7 +1552,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
